--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-observation-body-weight.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-observation-body-weight.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3229" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3571" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -217,13 +217,209 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Observation.implicitRules</t>
+    <t>Observation.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Observation.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Observation.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>Observation.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Observation.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -234,9 +430,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>Observation.language</t>
@@ -319,38 +512,10 @@
     <t>Observation.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Observation.extension:supportingInfo</t>
@@ -567,39 +732,16 @@
     <t>Observation.category.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -820,9 +962,6 @@
     <t>5. SHALL contain exactly one [1..1] code, where the @code SHOULD be selected from ValueSet HITSP Vital Sign Result Type 2.16.840.1.113883.3.88.12.80.62 DYNAMIC (CONF:7301).</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
@@ -1048,10 +1187,6 @@
     <t>Observation.issued</t>
   </si>
   <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
     <t>Date/Time this version was made available</t>
   </si>
   <si>
@@ -1407,9 +1542,6 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -2158,7 +2290,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP83"/>
+  <dimension ref="A1:AP92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.88671875" customWidth="true" bestFit="true"/>
@@ -2184,7 +2316,7 @@
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="69.1875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="21.17578125" customWidth="true" bestFit="true"/>
@@ -2583,10 +2715,10 @@
         <v>38</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>65</v>
@@ -2597,9 +2729,7 @@
       <c r="M4" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>68</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>38</v>
@@ -2648,7 +2778,7 @@
         <v>38</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>36</v>
@@ -2657,10 +2787,10 @@
         <v>49</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>38</v>
@@ -2672,7 +2802,7 @@
         <v>38</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>38</v>
@@ -2683,21 +2813,21 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>38</v>
@@ -2744,28 +2874,28 @@
         <v>38</v>
       </c>
       <c r="X5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB5" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="AC5" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Z5" t="s" s="2">
+      <c r="AD5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE5" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>79</v>
@@ -2774,13 +2904,13 @@
         <v>36</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>38</v>
@@ -2792,7 +2922,7 @@
         <v>38</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>38</v>
@@ -2803,14 +2933,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2826,19 +2956,19 @@
         <v>38</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2888,7 +3018,7 @@
         <v>38</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>36</v>
@@ -2912,7 +3042,7 @@
         <v>38</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>38</v>
@@ -2923,21 +3053,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>38</v>
@@ -2946,19 +3076,19 @@
         <v>38</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3008,19 +3138,19 @@
         <v>38</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>38</v>
@@ -3032,7 +3162,7 @@
         <v>38</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>38</v>
@@ -3043,21 +3173,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>38</v>
@@ -3066,19 +3196,19 @@
         <v>38</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3116,31 +3246,31 @@
         <v>38</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>38</v>
@@ -3152,7 +3282,7 @@
         <v>38</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>38</v>
@@ -3163,14 +3293,12 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>38</v>
       </c>
@@ -3179,7 +3307,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>38</v>
@@ -3188,18 +3316,20 @@
         <v>38</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>38</v>
@@ -3236,19 +3366,19 @@
         <v>38</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>36</v>
@@ -3260,7 +3390,7 @@
         <v>61</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>38</v>
@@ -3272,7 +3402,7 @@
         <v>38</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>38</v>
@@ -3283,46 +3413,46 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>98</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>38</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>38</v>
       </c>
@@ -3331,7 +3461,7 @@
         <v>38</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>38</v>
@@ -3358,19 +3488,19 @@
         <v>38</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>36</v>
@@ -3382,7 +3512,7 @@
         <v>61</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>38</v>
@@ -3394,7 +3524,7 @@
         <v>38</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>38</v>
@@ -3405,10 +3535,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3431,18 +3561,18 @@
         <v>50</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>120</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>38</v>
       </c>
@@ -3466,13 +3596,13 @@
         <v>38</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>38</v>
@@ -3505,19 +3635,19 @@
         <v>62</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>121</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>38</v>
@@ -3525,14 +3655,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3551,20 +3681,18 @@
         <v>50</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>38</v>
       </c>
@@ -3588,13 +3716,13 @@
         <v>38</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>38</v>
@@ -3612,7 +3740,7 @@
         <v>38</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>36</v>
@@ -3624,19 +3752,19 @@
         <v>61</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>38</v>
@@ -3647,42 +3775,42 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>137</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>50</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3732,31 +3860,31 @@
         <v>38</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>142</v>
+        <v>38</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>143</v>
+        <v>38</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>38</v>
@@ -3767,10 +3895,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3778,35 +3906,33 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>38</v>
       </c>
@@ -3830,13 +3956,13 @@
         <v>38</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>38</v>
@@ -3854,10 +3980,10 @@
         <v>38</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>49</v>
@@ -3869,19 +3995,19 @@
         <v>62</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>155</v>
+        <v>38</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>38</v>
@@ -3889,24 +4015,24 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G15" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="H15" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>38</v>
@@ -3915,20 +4041,18 @@
         <v>38</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>38</v>
       </c>
@@ -3952,35 +4076,37 @@
         <v>38</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>164</v>
+        <v>38</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>61</v>
@@ -3995,13 +4121,13 @@
         <v>38</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>169</v>
+        <v>38</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>38</v>
@@ -4009,26 +4135,24 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>38</v>
@@ -4037,20 +4161,18 @@
         <v>38</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>38</v>
       </c>
@@ -4074,13 +4196,13 @@
         <v>38</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>164</v>
+        <v>38</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>38</v>
@@ -4098,7 +4220,7 @@
         <v>38</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>36</v>
@@ -4107,10 +4229,10 @@
         <v>37</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>38</v>
@@ -4119,13 +4241,13 @@
         <v>38</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>169</v>
+        <v>38</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>38</v>
@@ -4133,21 +4255,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>38</v>
@@ -4159,15 +4281,17 @@
         <v>38</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>38</v>
@@ -4204,31 +4328,31 @@
         <v>38</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>38</v>
@@ -4240,7 +4364,7 @@
         <v>38</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>38</v>
@@ -4251,21 +4375,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>38</v>
@@ -4277,17 +4403,15 @@
         <v>38</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>38</v>
@@ -4324,19 +4448,19 @@
         <v>38</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
@@ -4348,7 +4472,7 @@
         <v>61</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>38</v>
@@ -4371,45 +4495,45 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>37</v>
       </c>
       <c r="H19" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I19" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="I19" t="s" s="2">
-        <v>38</v>
-      </c>
       <c r="J19" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>38</v>
@@ -4446,19 +4570,19 @@
         <v>38</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
@@ -4470,7 +4594,7 @@
         <v>61</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>38</v>
@@ -4479,10 +4603,10 @@
         <v>38</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>191</v>
+        <v>63</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>38</v>
@@ -4493,10 +4617,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4507,7 +4631,7 @@
         <v>36</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>38</v>
@@ -4516,19 +4640,21 @@
         <v>38</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>38</v>
       </c>
@@ -4576,34 +4702,34 @@
         <v>38</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>38</v>
@@ -4611,14 +4737,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4634,21 +4760,23 @@
         <v>38</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>38</v>
       </c>
@@ -4684,19 +4812,19 @@
         <v>38</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -4708,19 +4836,19 @@
         <v>61</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>38</v>
+        <v>186</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>38</v>
+        <v>187</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>38</v>
@@ -4731,24 +4859,24 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>38</v>
@@ -4757,26 +4885,24 @@
         <v>50</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>65</v>
+        <v>191</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>202</v>
+        <v>38</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>38</v>
@@ -4818,31 +4944,31 @@
         <v>38</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>38</v>
@@ -4853,10 +4979,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4864,33 +4990,35 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>50</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>38</v>
       </c>
@@ -4914,13 +5042,13 @@
         <v>38</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>38</v>
+        <v>203</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>38</v>
+        <v>204</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>38</v>
+        <v>205</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>38</v>
@@ -4938,10 +5066,10 @@
         <v>38</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>49</v>
@@ -4953,19 +5081,19 @@
         <v>62</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>38</v>
+        <v>206</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>38</v>
+        <v>207</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>38</v>
+        <v>210</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>38</v>
@@ -4973,10 +5101,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4987,7 +5115,7 @@
         <v>49</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>50</v>
@@ -4996,29 +5124,29 @@
         <v>38</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>220</v>
+        <v>38</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>38</v>
@@ -5036,37 +5164,35 @@
         <v>38</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>38</v>
+        <v>217</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>38</v>
+        <v>218</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>61</v>
@@ -5081,13 +5207,13 @@
         <v>38</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>38</v>
@@ -5095,45 +5221,47 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="B25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>38</v>
@@ -5158,13 +5286,13 @@
         <v>38</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>38</v>
+        <v>217</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>38</v>
+        <v>218</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>38</v>
@@ -5182,13 +5310,13 @@
         <v>38</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>61</v>
@@ -5203,13 +5331,13 @@
         <v>38</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>38</v>
@@ -5217,10 +5345,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5240,23 +5368,19 @@
         <v>38</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>234</v>
+        <v>65</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>66</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>38</v>
       </c>
@@ -5304,7 +5428,7 @@
         <v>38</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>68</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
@@ -5313,10 +5437,10 @@
         <v>49</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>38</v>
@@ -5325,10 +5449,10 @@
         <v>38</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>241</v>
+        <v>69</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>38</v>
@@ -5339,21 +5463,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>38</v>
@@ -5362,23 +5486,21 @@
         <v>38</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>73</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>245</v>
+        <v>74</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>38</v>
       </c>
@@ -5414,31 +5536,31 @@
         <v>38</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>38</v>
@@ -5447,10 +5569,10 @@
         <v>38</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>249</v>
+        <v>38</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>38</v>
@@ -5461,21 +5583,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>252</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>49</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>50</v>
@@ -5487,19 +5609,19 @@
         <v>50</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>38</v>
@@ -5524,13 +5646,13 @@
         <v>38</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>257</v>
+        <v>38</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>259</v>
+        <v>38</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>38</v>
@@ -5548,13 +5670,13 @@
         <v>38</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>61</v>
@@ -5563,30 +5685,30 @@
         <v>62</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>260</v>
+        <v>38</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>261</v>
+        <v>38</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>264</v>
+        <v>38</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>265</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5609,13 +5731,13 @@
         <v>38</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>175</v>
+        <v>66</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5666,7 +5788,7 @@
         <v>38</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>177</v>
+        <v>68</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
@@ -5690,7 +5812,7 @@
         <v>38</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>38</v>
@@ -5701,14 +5823,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5727,16 +5849,16 @@
         <v>38</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5774,19 +5896,19 @@
         <v>38</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>36</v>
@@ -5798,7 +5920,7 @@
         <v>61</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>38</v>
@@ -5821,10 +5943,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5832,13 +5954,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>38</v>
@@ -5847,26 +5969,26 @@
         <v>50</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>184</v>
+        <v>93</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>186</v>
+        <v>245</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>187</v>
+        <v>246</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>188</v>
+        <v>247</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>38</v>
+        <v>248</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>38</v>
@@ -5896,23 +6018,25 @@
         <v>38</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>61</v>
@@ -5927,10 +6051,10 @@
         <v>38</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>38</v>
@@ -5941,20 +6065,18 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>38</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>49</v>
@@ -5969,20 +6091,18 @@
         <v>50</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>38</v>
       </c>
@@ -6030,13 +6150,13 @@
         <v>38</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>61</v>
@@ -6051,10 +6171,10 @@
         <v>38</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>38</v>
@@ -6065,10 +6185,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6076,37 +6196,41 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>175</v>
+        <v>262</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>38</v>
+        <v>266</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>38</v>
@@ -6148,7 +6272,7 @@
         <v>38</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>177</v>
+        <v>267</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>36</v>
@@ -6157,10 +6281,10 @@
         <v>49</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>38</v>
@@ -6169,10 +6293,10 @@
         <v>38</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>38</v>
+        <v>268</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>70</v>
+        <v>269</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>38</v>
@@ -6183,21 +6307,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>38</v>
@@ -6206,21 +6330,23 @@
         <v>38</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>98</v>
+        <v>272</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>180</v>
+        <v>273</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>38</v>
       </c>
@@ -6256,31 +6382,31 @@
         <v>38</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>38</v>
@@ -6289,10 +6415,10 @@
         <v>38</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>38</v>
+        <v>276</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>63</v>
+        <v>277</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>38</v>
@@ -6303,10 +6429,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6314,7 +6440,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>49</v>
@@ -6329,26 +6455,26 @@
         <v>50</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>65</v>
+        <v>280</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>198</v>
+        <v>281</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>199</v>
+        <v>282</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>200</v>
+        <v>283</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>201</v>
+        <v>284</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>278</v>
+        <v>38</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>38</v>
@@ -6390,7 +6516,7 @@
         <v>38</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>203</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>36</v>
@@ -6411,10 +6537,10 @@
         <v>38</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>204</v>
+        <v>286</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>205</v>
+        <v>287</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>38</v>
@@ -6425,10 +6551,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6451,18 +6577,20 @@
         <v>50</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>208</v>
+        <v>290</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>209</v>
+        <v>291</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>38</v>
       </c>
@@ -6510,7 +6638,7 @@
         <v>38</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>211</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>36</v>
@@ -6531,10 +6659,10 @@
         <v>38</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>212</v>
+        <v>295</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>213</v>
+        <v>296</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>38</v>
@@ -6545,14 +6673,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>38</v>
+        <v>298</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6562,7 +6690,7 @@
         <v>49</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>38</v>
@@ -6571,26 +6699,26 @@
         <v>50</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>72</v>
+        <v>212</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>216</v>
+        <v>299</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>217</v>
+        <v>300</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>218</v>
+        <v>301</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>219</v>
+        <v>302</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>283</v>
+        <v>38</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>38</v>
@@ -6608,13 +6736,13 @@
         <v>38</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>38</v>
+        <v>303</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>38</v>
+        <v>304</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>38</v>
@@ -6632,10 +6760,10 @@
         <v>38</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>221</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>49</v>
@@ -6647,30 +6775,30 @@
         <v>62</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>38</v>
+        <v>305</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>38</v>
+        <v>306</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>223</v>
+        <v>308</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>38</v>
+        <v>309</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>38</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6690,23 +6818,19 @@
         <v>38</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>226</v>
+        <v>66</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>38</v>
       </c>
@@ -6754,7 +6878,7 @@
         <v>38</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>229</v>
+        <v>68</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>36</v>
@@ -6763,10 +6887,10 @@
         <v>49</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>38</v>
@@ -6775,10 +6899,10 @@
         <v>38</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>230</v>
+        <v>38</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>231</v>
+        <v>69</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>38</v>
@@ -6789,21 +6913,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>38</v>
@@ -6812,23 +6936,21 @@
         <v>38</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>234</v>
+        <v>72</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>236</v>
+        <v>74</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>38</v>
       </c>
@@ -6864,31 +6986,31 @@
         <v>38</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>38</v>
@@ -6897,10 +7019,10 @@
         <v>38</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>240</v>
+        <v>38</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>241</v>
+        <v>63</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>38</v>
@@ -6911,10 +7033,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6925,7 +7047,7 @@
         <v>36</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>38</v>
@@ -6937,19 +7059,19 @@
         <v>50</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>38</v>
@@ -6986,25 +7108,23 @@
         <v>38</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>61</v>
@@ -7019,10 +7139,10 @@
         <v>38</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>38</v>
@@ -7033,12 +7153,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>38</v>
       </c>
@@ -7050,7 +7172,7 @@
         <v>49</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>38</v>
@@ -7059,19 +7181,19 @@
         <v>50</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>290</v>
+        <v>109</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>291</v>
+        <v>231</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>293</v>
+        <v>233</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>294</v>
+        <v>234</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>38</v>
@@ -7120,34 +7242,34 @@
         <v>38</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>295</v>
+        <v>38</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>298</v>
+        <v>38</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>38</v>
@@ -7155,10 +7277,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7169,7 +7291,7 @@
         <v>36</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>38</v>
@@ -7178,20 +7300,18 @@
         <v>38</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>301</v>
+        <v>66</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>38</v>
@@ -7240,19 +7360,19 @@
         <v>38</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>299</v>
+        <v>68</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>38</v>
@@ -7261,13 +7381,13 @@
         <v>38</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>262</v>
+        <v>38</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>304</v>
+        <v>69</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>298</v>
+        <v>38</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>38</v>
@@ -7275,21 +7395,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>306</v>
+        <v>71</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>38</v>
@@ -7298,23 +7418,21 @@
         <v>38</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>307</v>
+        <v>72</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>308</v>
+        <v>73</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>309</v>
+        <v>74</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>38</v>
       </c>
@@ -7350,46 +7468,46 @@
         <v>38</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>312</v>
+        <v>38</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>313</v>
+        <v>38</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>314</v>
+        <v>63</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>315</v>
+        <v>38</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>38</v>
@@ -7397,14 +7515,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>317</v>
+        <v>38</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7414,7 +7532,7 @@
         <v>49</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>38</v>
@@ -7423,26 +7541,26 @@
         <v>50</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>318</v>
+        <v>93</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>319</v>
+        <v>244</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>321</v>
+        <v>246</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>322</v>
+        <v>247</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>38</v>
+        <v>323</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>38</v>
@@ -7484,7 +7602,7 @@
         <v>38</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>316</v>
+        <v>249</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>36</v>
@@ -7493,25 +7611,25 @@
         <v>49</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>323</v>
+        <v>61</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>324</v>
+        <v>62</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>325</v>
+        <v>38</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>327</v>
+        <v>251</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>328</v>
+        <v>38</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>38</v>
@@ -7519,10 +7637,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7545,16 +7663,16 @@
         <v>50</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>330</v>
+        <v>65</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>332</v>
+        <v>255</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>333</v>
+        <v>256</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7604,7 +7722,7 @@
         <v>38</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>329</v>
+        <v>257</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>36</v>
@@ -7625,13 +7743,13 @@
         <v>38</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>334</v>
+        <v>258</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>335</v>
+        <v>259</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>336</v>
+        <v>38</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>38</v>
@@ -7639,10 +7757,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7650,10 +7768,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>38</v>
@@ -7665,26 +7783,26 @@
         <v>50</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>338</v>
+        <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>339</v>
+        <v>262</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
+        <v>263</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>130</v>
+        <v>264</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>341</v>
+        <v>265</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>38</v>
+        <v>328</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>38</v>
@@ -7726,34 +7844,34 @@
         <v>38</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>337</v>
+        <v>267</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>342</v>
+        <v>38</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>343</v>
+        <v>268</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>344</v>
+        <v>269</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>345</v>
+        <v>38</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>38</v>
@@ -7761,10 +7879,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7778,7 +7896,7 @@
         <v>49</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>38</v>
@@ -7787,19 +7905,19 @@
         <v>50</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>347</v>
+        <v>65</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>348</v>
+        <v>272</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>348</v>
+        <v>273</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>349</v>
+        <v>264</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>350</v>
+        <v>274</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>38</v>
@@ -7836,17 +7954,19 @@
         <v>38</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AC47" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="AD47" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>352</v>
+        <v>38</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>346</v>
+        <v>275</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>36</v>
@@ -7855,7 +7975,7 @@
         <v>49</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>353</v>
+        <v>61</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>62</v>
@@ -7864,31 +7984,29 @@
         <v>38</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>354</v>
+        <v>38</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>355</v>
+        <v>276</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>356</v>
+        <v>277</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>357</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>38</v>
       </c>
@@ -7900,7 +8018,7 @@
         <v>49</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>38</v>
@@ -7909,19 +8027,19 @@
         <v>50</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>348</v>
+        <v>281</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>349</v>
+        <v>283</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>350</v>
+        <v>284</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>38</v>
@@ -7970,7 +8088,7 @@
         <v>38</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>346</v>
+        <v>285</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>36</v>
@@ -7979,7 +8097,7 @@
         <v>49</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>353</v>
+        <v>61</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>62</v>
@@ -7988,27 +8106,27 @@
         <v>38</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>354</v>
+        <v>38</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>355</v>
+        <v>286</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>356</v>
+        <v>287</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>357</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8028,19 +8146,23 @@
         <v>38</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>175</v>
+        <v>290</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>38</v>
       </c>
@@ -8088,7 +8210,7 @@
         <v>38</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>36</v>
@@ -8097,10 +8219,10 @@
         <v>49</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>38</v>
@@ -8109,10 +8231,10 @@
         <v>38</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>38</v>
+        <v>295</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>70</v>
+        <v>296</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>38</v>
@@ -8123,44 +8245,46 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>97</v>
+        <v>335</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>98</v>
+        <v>336</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>180</v>
+        <v>337</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>38</v>
       </c>
@@ -8196,46 +8320,46 @@
         <v>38</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>181</v>
+        <v>334</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>38</v>
+        <v>341</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>63</v>
+        <v>342</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>38</v>
+        <v>343</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>38</v>
@@ -8243,10 +8367,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8254,13 +8378,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>38</v>
@@ -8269,20 +8393,18 @@
         <v>50</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>38</v>
       </c>
@@ -8330,19 +8452,19 @@
         <v>38</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>38</v>
@@ -8351,13 +8473,13 @@
         <v>38</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>373</v>
+        <v>307</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>38</v>
+        <v>343</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>38</v>
@@ -8365,14 +8487,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>38</v>
+        <v>351</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8385,32 +8507,30 @@
         <v>38</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>50</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>72</v>
+        <v>352</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>218</v>
+        <v>355</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="Q52" t="s" s="2">
-        <v>380</v>
-      </c>
+      <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
         <v>38</v>
       </c>
@@ -8430,13 +8550,13 @@
         <v>38</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>381</v>
+        <v>38</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>382</v>
+        <v>38</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>38</v>
@@ -8454,7 +8574,7 @@
         <v>38</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>383</v>
+        <v>350</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -8466,22 +8586,22 @@
         <v>61</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>38</v>
+        <v>357</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>38</v>
+        <v>360</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>38</v>
@@ -8489,14 +8609,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>38</v>
+        <v>362</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8515,19 +8635,19 @@
         <v>50</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>174</v>
+        <v>363</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>218</v>
+        <v>366</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>38</v>
@@ -8576,7 +8696,7 @@
         <v>38</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -8585,25 +8705,25 @@
         <v>49</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>61</v>
+        <v>368</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>62</v>
+        <v>369</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>38</v>
+        <v>370</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>38</v>
+        <v>373</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>38</v>
@@ -8611,10 +8731,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8622,13 +8742,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>38</v>
@@ -8637,26 +8757,24 @@
         <v>50</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>400</v>
+        <v>38</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>38</v>
@@ -8698,7 +8816,7 @@
         <v>38</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
@@ -8707,7 +8825,7 @@
         <v>49</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>402</v>
+        <v>61</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>62</v>
@@ -8719,13 +8837,13 @@
         <v>38</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>38</v>
+        <v>380</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>38</v>
@@ -8733,10 +8851,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8744,13 +8862,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>38</v>
@@ -8759,19 +8877,19 @@
         <v>50</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>72</v>
+        <v>382</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>407</v>
+        <v>183</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>38</v>
@@ -8796,13 +8914,13 @@
         <v>38</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>409</v>
+        <v>38</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>410</v>
+        <v>38</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>38</v>
@@ -8820,34 +8938,34 @@
         <v>38</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>38</v>
+        <v>386</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>38</v>
+        <v>389</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>38</v>
@@ -8855,10 +8973,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8878,22 +8996,22 @@
         <v>38</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>159</v>
+        <v>391</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>38</v>
@@ -8918,31 +9036,29 @@
         <v>38</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>257</v>
+        <v>38</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>418</v>
+        <v>38</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>419</v>
+        <v>38</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>38</v>
+        <v>396</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
@@ -8951,7 +9067,7 @@
         <v>49</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>62</v>
@@ -8960,62 +9076,64 @@
         <v>38</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>38</v>
+        <v>398</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>63</v>
+        <v>399</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>38</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>423</v>
+        <v>38</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>159</v>
+        <v>404</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>424</v>
+        <v>392</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>427</v>
+        <v>394</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>38</v>
@@ -9040,13 +9158,13 @@
         <v>38</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>257</v>
+        <v>38</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>428</v>
+        <v>38</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>429</v>
+        <v>38</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>38</v>
@@ -9064,16 +9182,16 @@
         <v>38</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>422</v>
+        <v>390</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>61</v>
+        <v>397</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>62</v>
@@ -9082,27 +9200,27 @@
         <v>38</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>431</v>
+        <v>399</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>432</v>
+        <v>400</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>433</v>
+        <v>401</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>406</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9113,7 +9231,7 @@
         <v>36</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>38</v>
@@ -9125,20 +9243,16 @@
         <v>38</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>435</v>
+        <v>65</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>436</v>
+        <v>66</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>38</v>
       </c>
@@ -9186,19 +9300,19 @@
         <v>38</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>68</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>38</v>
@@ -9207,10 +9321,10 @@
         <v>38</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>440</v>
+        <v>38</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>441</v>
+        <v>69</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>38</v>
@@ -9221,21 +9335,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>442</v>
+        <v>407</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>442</v>
+        <v>408</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>38</v>
@@ -9247,16 +9361,16 @@
         <v>38</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>443</v>
+        <v>73</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>444</v>
+        <v>74</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>445</v>
+        <v>75</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9282,69 +9396,69 @@
         <v>38</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>446</v>
+        <v>38</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>447</v>
+        <v>38</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>448</v>
+        <v>38</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>442</v>
+        <v>79</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>449</v>
+        <v>38</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>450</v>
+        <v>38</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>451</v>
+        <v>63</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>452</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9352,34 +9466,34 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>159</v>
+        <v>411</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>454</v>
+        <v>412</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>455</v>
+        <v>413</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>456</v>
+        <v>414</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>457</v>
+        <v>415</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>38</v>
@@ -9404,11 +9518,13 @@
         <v>38</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>38</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>458</v>
+        <v>38</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>38</v>
@@ -9426,7 +9542,7 @@
         <v>38</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
@@ -9447,10 +9563,10 @@
         <v>38</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>459</v>
+        <v>417</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>460</v>
+        <v>418</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>38</v>
@@ -9461,10 +9577,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>461</v>
+        <v>419</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9481,28 +9597,32 @@
         <v>38</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>462</v>
+        <v>133</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="Q61" s="2"/>
+      <c r="Q61" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="R61" t="s" s="2">
         <v>38</v>
       </c>
@@ -9522,13 +9642,13 @@
         <v>38</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>38</v>
+        <v>203</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>38</v>
+        <v>425</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>38</v>
+        <v>426</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>38</v>
@@ -9546,7 +9666,7 @@
         <v>38</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>461</v>
+        <v>427</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
@@ -9558,33 +9678,33 @@
         <v>61</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>466</v>
+        <v>38</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>468</v>
+        <v>429</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>469</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>470</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9592,33 +9712,35 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>471</v>
+        <v>65</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>472</v>
+        <v>432</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>473</v>
+        <v>433</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>38</v>
       </c>
@@ -9666,7 +9788,7 @@
         <v>38</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -9678,33 +9800,33 @@
         <v>61</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>475</v>
+        <v>38</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>476</v>
+        <v>436</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>477</v>
+        <v>437</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>478</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>479</v>
+        <v>438</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
+        <v>439</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9712,41 +9834,41 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>480</v>
+        <v>93</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>481</v>
+        <v>440</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>38</v>
+        <v>444</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>38</v>
@@ -9788,19 +9910,19 @@
         <v>38</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>479</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>61</v>
+        <v>446</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>485</v>
+        <v>62</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>38</v>
@@ -9809,10 +9931,10 @@
         <v>38</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>486</v>
+        <v>436</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>487</v>
+        <v>447</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>38</v>
@@ -9823,10 +9945,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>488</v>
+        <v>448</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9834,31 +9956,35 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>49</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>175</v>
+        <v>450</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>38</v>
       </c>
@@ -9882,13 +10008,13 @@
         <v>38</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>38</v>
+        <v>203</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>38</v>
+        <v>453</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>38</v>
+        <v>454</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>38</v>
@@ -9906,7 +10032,7 @@
         <v>38</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>177</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
@@ -9915,10 +10041,10 @@
         <v>49</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>38</v>
@@ -9927,10 +10053,10 @@
         <v>38</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>38</v>
+        <v>436</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>70</v>
+        <v>456</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>38</v>
@@ -9941,24 +10067,24 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>38</v>
@@ -9967,18 +10093,20 @@
         <v>38</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>97</v>
+        <v>212</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>98</v>
+        <v>458</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>180</v>
+        <v>459</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>38</v>
       </c>
@@ -10002,43 +10130,43 @@
         <v>38</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>38</v>
+        <v>462</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>38</v>
+        <v>463</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>181</v>
+        <v>457</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>61</v>
+        <v>464</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>38</v>
@@ -10047,10 +10175,10 @@
         <v>38</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>63</v>
+        <v>465</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>38</v>
@@ -10061,14 +10189,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>491</v>
+        <v>467</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10081,25 +10209,25 @@
         <v>38</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>97</v>
+        <v>212</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>100</v>
+        <v>470</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>114</v>
+        <v>471</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>38</v>
@@ -10124,13 +10252,13 @@
         <v>38</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>38</v>
+        <v>472</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>38</v>
+        <v>473</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>38</v>
@@ -10148,7 +10276,7 @@
         <v>38</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>494</v>
+        <v>466</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
@@ -10160,33 +10288,33 @@
         <v>61</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>38</v>
+        <v>474</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>38</v>
+        <v>475</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>63</v>
+        <v>476</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>38</v>
+        <v>477</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10197,7 +10325,7 @@
         <v>36</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>38</v>
@@ -10209,18 +10337,20 @@
         <v>38</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>38</v>
       </c>
@@ -10268,19 +10398,19 @@
         <v>38</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>500</v>
+        <v>61</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>501</v>
+        <v>62</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>38</v>
@@ -10289,10 +10419,10 @@
         <v>38</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>38</v>
@@ -10303,10 +10433,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10329,16 +10459,16 @@
         <v>38</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>496</v>
+        <v>212</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10364,13 +10494,13 @@
         <v>38</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>38</v>
+        <v>490</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>38</v>
+        <v>491</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>38</v>
@@ -10388,7 +10518,7 @@
         <v>38</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
@@ -10397,36 +10527,36 @@
         <v>49</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>500</v>
+        <v>61</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>501</v>
+        <v>62</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>38</v>
+        <v>492</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>38</v>
+        <v>495</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10449,19 +10579,19 @@
         <v>38</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>38</v>
@@ -10486,13 +10616,11 @@
         <v>38</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>38</v>
@@ -10510,7 +10638,7 @@
         <v>38</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
@@ -10528,13 +10656,13 @@
         <v>38</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>515</v>
+        <v>38</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>432</v>
+        <v>503</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>38</v>
@@ -10545,10 +10673,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10559,7 +10687,7 @@
         <v>36</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>38</v>
@@ -10571,20 +10699,18 @@
         <v>38</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>159</v>
+        <v>505</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>38</v>
       </c>
@@ -10608,13 +10734,13 @@
         <v>38</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>446</v>
+        <v>38</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>522</v>
+        <v>38</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>523</v>
+        <v>38</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>38</v>
@@ -10632,45 +10758,45 @@
         <v>38</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>432</v>
+        <v>511</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>38</v>
+        <v>512</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10693,20 +10819,18 @@
         <v>38</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>38</v>
       </c>
@@ -10754,7 +10878,7 @@
         <v>38</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -10766,33 +10890,33 @@
         <v>61</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>530</v>
+        <v>185</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>38</v>
+        <v>518</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>38</v>
+        <v>521</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10803,7 +10927,7 @@
         <v>36</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>38</v>
@@ -10815,18 +10939,20 @@
         <v>38</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>174</v>
+        <v>523</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>527</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>38</v>
       </c>
@@ -10874,19 +11000,19 @@
         <v>38</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>62</v>
+        <v>528</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>38</v>
@@ -10895,10 +11021,10 @@
         <v>38</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>38</v>
@@ -10909,10 +11035,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10923,7 +11049,7 @@
         <v>36</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>38</v>
@@ -10932,20 +11058,18 @@
         <v>38</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>538</v>
+        <v>65</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>539</v>
+        <v>66</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>38</v>
@@ -10994,19 +11118,19 @@
         <v>38</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>537</v>
+        <v>68</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>38</v>
@@ -11015,10 +11139,10 @@
         <v>38</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>542</v>
+        <v>38</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>543</v>
+        <v>69</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>38</v>
@@ -11029,14 +11153,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11052,19 +11176,19 @@
         <v>38</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>545</v>
+        <v>72</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>546</v>
+        <v>73</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>547</v>
+        <v>74</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>548</v>
+        <v>75</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11102,19 +11226,19 @@
         <v>38</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>544</v>
+        <v>79</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -11126,7 +11250,7 @@
         <v>61</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>38</v>
@@ -11135,10 +11259,10 @@
         <v>38</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>542</v>
+        <v>38</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>549</v>
+        <v>63</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>38</v>
@@ -11149,14 +11273,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>38</v>
+        <v>534</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11166,28 +11290,28 @@
         <v>37</v>
       </c>
       <c r="H75" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I75" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>50</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>480</v>
+        <v>72</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>552</v>
+        <v>75</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>553</v>
+        <v>167</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>38</v>
@@ -11236,7 +11360,7 @@
         <v>38</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -11248,7 +11372,7 @@
         <v>61</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>554</v>
+        <v>80</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>38</v>
@@ -11257,10 +11381,10 @@
         <v>38</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>555</v>
+        <v>38</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>556</v>
+        <v>63</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>38</v>
@@ -11271,10 +11395,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11297,15 +11421,17 @@
         <v>38</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>174</v>
+        <v>539</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>175</v>
+        <v>540</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>541</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>38</v>
@@ -11354,7 +11480,7 @@
         <v>38</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>177</v>
+        <v>538</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
@@ -11363,10 +11489,10 @@
         <v>49</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>38</v>
+        <v>543</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>38</v>
+        <v>544</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>38</v>
@@ -11375,10 +11501,10 @@
         <v>38</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>38</v>
+        <v>545</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>70</v>
+        <v>546</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>38</v>
@@ -11389,21 +11515,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>38</v>
@@ -11415,16 +11541,16 @@
         <v>38</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>97</v>
+        <v>539</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>98</v>
+        <v>548</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>180</v>
+        <v>549</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>100</v>
+        <v>542</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11462,31 +11588,31 @@
         <v>38</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>181</v>
+        <v>547</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>61</v>
+        <v>543</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>105</v>
+        <v>544</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>38</v>
@@ -11495,10 +11621,10 @@
         <v>38</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>38</v>
+        <v>545</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>63</v>
+        <v>550</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>38</v>
@@ -11509,45 +11635,45 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>491</v>
+        <v>38</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>38</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>97</v>
+        <v>212</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>492</v>
+        <v>552</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>493</v>
+        <v>553</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>100</v>
+        <v>554</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>114</v>
+        <v>555</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>38</v>
@@ -11572,13 +11698,13 @@
         <v>38</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>38</v>
+        <v>556</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>38</v>
+        <v>557</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>38</v>
@@ -11596,31 +11722,31 @@
         <v>38</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>494</v>
+        <v>551</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>61</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>38</v>
+        <v>558</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>38</v>
+        <v>559</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>63</v>
+        <v>476</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>38</v>
@@ -11642,22 +11768,22 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>561</v>
@@ -11694,13 +11820,13 @@
         <v>38</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>257</v>
+        <v>123</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>258</v>
+        <v>565</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>259</v>
+        <v>566</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>38</v>
@@ -11721,10 +11847,10 @@
         <v>560</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>61</v>
@@ -11736,16 +11862,16 @@
         <v>38</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>262</v>
+        <v>559</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>263</v>
+        <v>476</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>264</v>
+        <v>38</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>38</v>
@@ -11753,10 +11879,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11770,28 +11896,28 @@
         <v>49</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>38</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>347</v>
+        <v>568</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>350</v>
+        <v>572</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>38</v>
@@ -11816,13 +11942,13 @@
         <v>38</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>570</v>
+        <v>38</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>571</v>
+        <v>38</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>38</v>
@@ -11840,7 +11966,7 @@
         <v>38</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>36</v>
@@ -11849,36 +11975,36 @@
         <v>49</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>572</v>
+        <v>61</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>62</v>
+        <v>573</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>573</v>
+        <v>38</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>355</v>
+        <v>574</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>356</v>
+        <v>575</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>357</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11892,7 +12018,7 @@
         <v>49</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>38</v>
@@ -11901,20 +12027,18 @@
         <v>38</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>38</v>
       </c>
@@ -11938,13 +12062,13 @@
         <v>38</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>257</v>
+        <v>38</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>418</v>
+        <v>38</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>419</v>
+        <v>38</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>38</v>
@@ -11962,7 +12086,7 @@
         <v>38</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>36</v>
@@ -11971,7 +12095,7 @@
         <v>49</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>578</v>
+        <v>61</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>62</v>
@@ -11983,10 +12107,10 @@
         <v>38</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>63</v>
+        <v>545</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>421</v>
+        <v>579</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>38</v>
@@ -11997,14 +12121,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>423</v>
+        <v>38</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12020,23 +12144,21 @@
         <v>38</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>159</v>
+        <v>581</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>424</v>
+        <v>582</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>425</v>
+        <v>583</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>38</v>
       </c>
@@ -12060,13 +12182,13 @@
         <v>38</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>257</v>
+        <v>38</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>428</v>
+        <v>38</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>429</v>
+        <v>38</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>38</v>
@@ -12084,7 +12206,7 @@
         <v>38</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
@@ -12096,33 +12218,33 @@
         <v>61</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>430</v>
+        <v>38</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>431</v>
+        <v>585</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>432</v>
+        <v>586</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>433</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12142,23 +12264,21 @@
         <v>38</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>39</v>
+        <v>588</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>38</v>
       </c>
@@ -12206,7 +12326,7 @@
         <v>38</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>36</v>
@@ -12215,10 +12335,10 @@
         <v>37</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>38</v>
@@ -12227,20 +12347,1112 @@
         <v>38</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>486</v>
+        <v>585</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>487</v>
+        <v>592</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AP83" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP83">
+  <autoFilter ref="A1:AP92">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12250,7 +13462,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI82">
+  <conditionalFormatting sqref="A2:AI91">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
